--- a/E5_Tableau_synthese_Kittaneh.xlsx
+++ b/E5_Tableau_synthese_Kittaneh.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{533C5518-839C-4EE6-9FED-B7A2B94C2590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D7F5D4-D66D-47B5-AB9B-1A223675956C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,16 +19,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E5'!$A$1:$H$35</definedName>
   </definedNames>
   <calcPr calcId="0" iterateDelta="1E-4"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="67">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -131,16 +126,10 @@
 (Installation et configuration d'un serveur HTTP Apache, MariaDB, PHP, ProFTPD sur Debian Server 10)</t>
   </si>
   <si>
-    <t>2023-2024</t>
+    <t>2024-2025</t>
   </si>
   <si>
     <t>—</t>
-  </si>
-  <si>
-    <t>⚠ 3.3
-Participer à l'évolution d'un site Web
-(infrastructure serveur web, accès client)
-→ Limite : infrastructure ≠ contenu/CMS</t>
   </si>
   <si>
     <t>✔ 5.1 Tests intégration
@@ -175,7 +164,7 @@
 (Infra virtualisée 3 nœuds, NFS TrueNAS, HA, gestion utilisateurs/pools/rôles)</t>
   </si>
   <si>
-    <t>2024-2025</t>
+    <t>2025-2026</t>
   </si>
   <si>
     <t>✔ 1.1 Recenser/identifier les ressources
@@ -228,7 +217,7 @@
 (Mise en place d'une veille informationnelle active : flux RSS, newsletters tech, blogs SISR/cybersécurité, suivi des évolutions des technologies réseau et système)</t>
   </si>
   <si>
-    <t>2023-2025</t>
+    <t>2024-2026</t>
   </si>
   <si>
     <t>✔ 6.1 Environnement d'apprentissage personnel
@@ -250,7 +239,21 @@
     <t>Réalisations en milieu professionnel en cours de première année</t>
   </si>
   <si>
-    <t>(Aucune situation de stage 1ère année renseignée à ce jour)</t>
+    <t>Stage Repit Ainay
+(Réparation smartphones, Mac, PC · Diagnostic pannes matérielles/logicielles · Réinstallation OS Windows/macOS · Accompagnement client)</t>
+  </si>
+  <si>
+    <t>Stage 2025</t>
+  </si>
+  <si>
+    <t>✔ 2.1 Collecter, suivre et orienter des demandes
+(réception appareils clients, suivi des réparations, orientation vers le bon technicien)
+✔ 2.2 Traiter demandes réseau/système/applicatifs
+(diagnostic pannes matérielles et logicielles, réinstallation OS, configuration initiale)</t>
+  </si>
+  <si>
+    <t>✔ 5.3 Accompagner les utilisateurs
+(explication des interventions réalisées, conseils entretien, restitution du matériel)</t>
   </si>
   <si>
     <t>Réalisations en milieu professionnel en cours de seconde année</t>
@@ -261,7 +264,7 @@
   </si>
   <si>
     <t>Stage APE Conseil
-2024-2025</t>
+2025-2026</t>
   </si>
   <si>
     <t>✔ 1.1 Recenser/identifier les ressources
@@ -272,12 +275,6 @@
 (RDS centralisé, partages sur SRVAPPLI25, structure AD)</t>
   </si>
   <si>
-    <t>⚠ 4.1 Analyser objectifs/organisation
-(progression logique : serveur→AD→partages→GPO→RDS)
-⚠ 4.2 Planifier les activités
-(enchaînement des étapes — manque planning explicite)</t>
-  </si>
-  <si>
     <t>✔ 5.1 Tests intégration
 (connexion utilisateur, lecteur réseau, bureaux RDS séparés)
 ✔ 5.2 Déployer un service
@@ -312,6 +309,18 @@
 (vérification script exécuté, Windows activé, logiciels installés)
 ✔ 5.2 Déployer un service
 (~30 postes PXE/WDS + PowerShell — cœur de la situation)</t>
+  </si>
+  <si>
+    <t>✔ 3.3
+Participer à l'évolution d'un site Web
+(infrastructure serveur web, accès client)
+→ Limite : infrastructure ≠ contenu/CMS</t>
+  </si>
+  <si>
+    <t>✔ 4.1 Analyser objectifs/organisation
+(progression logique : serveur→AD→partages→GPO→RDS)
+✔ 4.2 Planifier les activités
+(enchaînement des étapes — manque planning explicite)</t>
   </si>
 </sst>
 </file>
@@ -321,7 +330,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* \-??\ [$€-1]_-"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -423,8 +432,17 @@
       <name val="Cambria"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Cambria"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Cambria"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -439,18 +457,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFBCE6B6"/>
         <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFBCE6B6"/>
         <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBCE6B6"/>
+        <bgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="19">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -712,6 +736,104 @@
         <color theme="2" tint="-0.749992370372631"/>
       </top>
       <bottom style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom style="thin">
         <color theme="2" tint="-0.749992370372631"/>
       </bottom>
       <diagonal/>
@@ -723,131 +845,152 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Euro" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Euro 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Euro" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Euro 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Normal 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -918,6 +1061,9 @@
       <rgbColor rgb="00333399"/>
       <rgbColor rgb="00333333"/>
     </indexedColors>
+    <mruColors>
+      <color rgb="FFBCE6B6"/>
+    </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1115,603 +1261,597 @@
   <dimension ref="A1:AQ35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="70.44140625" style="10" customWidth="1"/>
-    <col min="2" max="2" width="10.88671875" style="10"/>
-    <col min="3" max="8" width="18.6640625" style="10" customWidth="1"/>
+    <col min="1" max="1" width="70.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.88671875" style="1" customWidth="1"/>
+    <col min="3" max="8" width="18.6640625" style="1" customWidth="1"/>
     <col min="9" max="43" width="11.44140625" customWidth="1"/>
-    <col min="44" max="16384" width="10.88671875" style="10"/>
+    <col min="44" max="44" width="10.88671875" style="1" customWidth="1"/>
+    <col min="45" max="16384" width="10.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9" t="s">
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="9"/>
+      <c r="H1" s="37"/>
     </row>
     <row r="2" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
     </row>
     <row r="3" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="7" t="s">
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="44"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="11" t="s">
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="41"/>
     </row>
     <row r="6" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="17"/>
-    </row>
-    <row r="7" spans="1:13" s="20" customFormat="1" ht="324.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="18" t="s">
+      <c r="J6" s="8"/>
+    </row>
+    <row r="7" spans="1:13" s="11" customFormat="1" ht="324.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="50"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="J7" s="21"/>
-    </row>
-    <row r="8" spans="1:13" s="20" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="J7" s="12"/>
+    </row>
+    <row r="8" spans="1:13" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="J8" s="21"/>
-    </row>
-    <row r="9" spans="1:13" s="20" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="22" t="s">
+      <c r="B8" s="43"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="48"/>
+      <c r="J8" s="12"/>
+    </row>
+    <row r="9" spans="1:13" s="11" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="23"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="26"/>
-      <c r="J9" s="21"/>
-    </row>
-    <row r="10" spans="1:13" s="20" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="27" t="s">
+      <c r="B9" s="14"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="17"/>
+      <c r="J9" s="12"/>
+    </row>
+    <row r="10" spans="1:13" s="11" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="30" t="s">
+      <c r="C10" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="G10" s="31" t="s">
+      <c r="H10" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10" s="12"/>
+    </row>
+    <row r="11" spans="1:13" s="11" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="H10" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="J10" s="21"/>
-    </row>
-    <row r="11" spans="1:13" s="20" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="27" t="s">
+      <c r="B11" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="31" t="s">
+      <c r="D11" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="31" t="s">
+      <c r="E11" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" s="31" t="s">
+      <c r="H11" s="20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" s="11" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="H11" s="29" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" s="20" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="22" t="s">
+      <c r="B12" s="14"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="17"/>
+    </row>
+    <row r="13" spans="1:13" s="11" customFormat="1" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="23"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="26"/>
-    </row>
-    <row r="13" spans="1:13" s="20" customFormat="1" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="27" t="s">
+      <c r="B13" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="C13" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="31" t="s">
+      <c r="D13" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F13" s="31" t="s">
+      <c r="G13" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="31" t="s">
+      <c r="H13" s="20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" s="11" customFormat="1" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="H13" s="29" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" s="20" customFormat="1" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="27" t="s">
+      <c r="B14" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="31" t="s">
+      <c r="D14" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="31" t="s">
+      <c r="E14" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F14" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="G14" s="31" t="s">
+      <c r="H14" s="20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" s="11" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="H14" s="29" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" s="20" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="27" t="s">
+      <c r="B15" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="28" t="s">
+      <c r="C15" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="G15" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="H15" s="31" t="s">
+    </row>
+    <row r="16" spans="1:13" s="11" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="18" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" s="20" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="27" t="s">
+      <c r="B16" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="H16" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="B16" s="28" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="G16" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="H16" s="31" t="s">
+    </row>
+    <row r="17" spans="1:8" s="11" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="13"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="17"/>
+    </row>
+    <row r="18" spans="1:8" s="11" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="13"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="17"/>
+    </row>
+    <row r="19" spans="1:8" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="38" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" s="20" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="22"/>
-      <c r="B17" s="23"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="26"/>
-    </row>
-    <row r="18" spans="1:8" s="20" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="22"/>
-      <c r="B18" s="23"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="26"/>
-    </row>
-    <row r="19" spans="1:8" s="20" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="35"/>
+    </row>
+    <row r="20" spans="1:8" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-    </row>
-    <row r="20" spans="1:8" s="20" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="28" t="s">
+      <c r="B20" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="E20" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="G20" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="H20" s="29" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" s="20" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="22"/>
-      <c r="B21" s="23"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="26"/>
-    </row>
-    <row r="22" spans="1:8" s="20" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="22"/>
-      <c r="B22" s="23"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="26"/>
-    </row>
-    <row r="23" spans="1:8" s="20" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="22"/>
-      <c r="B23" s="23"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="26"/>
-    </row>
-    <row r="24" spans="1:8" s="20" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="22"/>
-      <c r="B24" s="23"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="26"/>
-    </row>
-    <row r="25" spans="1:8" s="20" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="22"/>
-      <c r="B25" s="23"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="26"/>
-    </row>
-    <row r="26" spans="1:8" s="20" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="22"/>
-      <c r="B26" s="23"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="26"/>
-    </row>
-    <row r="27" spans="1:8" s="20" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+      <c r="C20" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-    </row>
-    <row r="28" spans="1:8" s="20" customFormat="1" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="27" t="s">
+      <c r="E20" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" s="52" t="s">
         <v>53</v>
       </c>
-      <c r="B28" s="28" t="s">
+      <c r="H20" s="32" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" s="11" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="13"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="17"/>
+    </row>
+    <row r="22" spans="1:8" s="11" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="13"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="17"/>
+    </row>
+    <row r="23" spans="1:8" s="11" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="13"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="17"/>
+    </row>
+    <row r="24" spans="1:8" s="11" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="13"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="17"/>
+    </row>
+    <row r="25" spans="1:8" s="11" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="13"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="17"/>
+    </row>
+    <row r="26" spans="1:8" s="11" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="13"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="17"/>
+    </row>
+    <row r="27" spans="1:8" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="C28" s="31" t="s">
+      <c r="B27" s="34"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="35"/>
+    </row>
+    <row r="28" spans="1:8" s="11" customFormat="1" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="D28" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="E28" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F28" s="30" t="s">
+      <c r="B28" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="G28" s="31" t="s">
+      <c r="C28" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="H28" s="29" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" s="20" customFormat="1" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="27" t="s">
+      <c r="D28" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="F28" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="G28" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="C29" s="31" t="s">
+      <c r="H28" s="20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" s="11" customFormat="1" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="D29" s="31" t="s">
+      <c r="B29" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="E29" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F29" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="G29" s="31" t="s">
+      <c r="D29" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="H29" s="29" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" s="20" customFormat="1" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="27" t="s">
+      <c r="E29" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G29" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="B30" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="C30" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="D30" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="E30" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="F30" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="G30" s="31" t="s">
+      <c r="H29" s="20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" s="11" customFormat="1" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="H30" s="29" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" s="20" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="22"/>
-      <c r="B31" s="23"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="26"/>
-    </row>
-    <row r="32" spans="1:8" s="20" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="22"/>
-      <c r="B32" s="23"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="26"/>
-    </row>
-    <row r="33" spans="1:8" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="32"/>
-      <c r="B33"/>
-      <c r="C33"/>
-      <c r="D33"/>
-      <c r="E33"/>
-      <c r="F33"/>
-      <c r="G33"/>
-      <c r="H33"/>
-    </row>
-    <row r="34" spans="1:8" s="20" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="33"/>
-      <c r="B34" s="34"/>
-      <c r="C34" s="35"/>
-      <c r="D34" s="35"/>
-      <c r="E34" s="35"/>
-      <c r="F34" s="35"/>
-      <c r="G34" s="35"/>
-      <c r="H34" s="36"/>
-    </row>
-    <row r="35" spans="1:8" s="20" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="37"/>
-      <c r="B35" s="38"/>
-      <c r="C35" s="39"/>
-      <c r="D35" s="39"/>
-      <c r="E35" s="39"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="39"/>
-      <c r="H35" s="39"/>
+      <c r="B30" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D30" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G30" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="H30" s="20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" s="11" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="13"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="17"/>
+    </row>
+    <row r="32" spans="1:8" s="11" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="13"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="17"/>
+    </row>
+    <row r="33" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="21"/>
+    </row>
+    <row r="34" spans="1:8" s="11" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="22"/>
+      <c r="B34" s="23"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24"/>
+      <c r="H34" s="25"/>
+    </row>
+    <row r="35" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="26"/>
+      <c r="B35" s="27"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A19:H19"/>
     <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="G1:H1"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:H1"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A5:H5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.196527777777778" right="0.196527777777778" top="0.196527777777778" bottom="0.196527777777778" header="0.511811023622047" footer="0.511811023622047"/>

--- a/E5_Tableau_synthese_Kittaneh.xlsx
+++ b/E5_Tableau_synthese_Kittaneh.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fcc20703946d8efe/Documents/portfolio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D7F5D4-D66D-47B5-AB9B-1A223675956C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{C7D7F5D4-D66D-47B5-AB9B-1A223675956C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE7D729E-60D9-44FD-B796-68193BBE57C3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -433,13 +433,15 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
       <sz val="10"/>
       <name val="Cambria"/>
     </font>
     <font>
+      <u/>
       <sz val="10"/>
-      <name val="Cambria"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -839,11 +841,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -898,9 +901,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -937,31 +937,17 @@
     <xf numFmtId="0" fontId="15" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -982,13 +968,31 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="Euro" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Euro 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Lien hypertexte" xfId="4" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
@@ -1270,56 +1274,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="36" t="s">
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="37"/>
+      <c r="H1" s="47"/>
     </row>
     <row r="2" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
     </row>
     <row r="3" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="42" t="s">
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="43"/>
-      <c r="H3" s="44"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="37"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="35"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="34"/>
       <c r="F4" s="2" t="s">
         <v>6</v>
       </c>
@@ -1331,22 +1335,22 @@
       </c>
     </row>
     <row r="5" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="41"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="50"/>
     </row>
     <row r="6" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="45" t="s">
+      <c r="B6" s="38" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="5" t="s">
@@ -1370,8 +1374,8 @@
       <c r="J6" s="8"/>
     </row>
     <row r="7" spans="1:13" s="11" customFormat="1" ht="324.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="50"/>
-      <c r="B7" s="46"/>
+      <c r="A7" s="43"/>
+      <c r="B7" s="39"/>
       <c r="C7" s="9" t="s">
         <v>18</v>
       </c>
@@ -1393,16 +1397,16 @@
       <c r="J7" s="12"/>
     </row>
     <row r="8" spans="1:13" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="47" t="s">
+      <c r="A8" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="43"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="48"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="41"/>
       <c r="J8" s="12"/>
     </row>
     <row r="9" spans="1:13" s="11" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1419,55 +1423,55 @@
       <c r="J9" s="12"/>
     </row>
     <row r="10" spans="1:13" s="11" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="29" t="s">
+      <c r="C10" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="F10" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="G10" s="30" t="s">
+      <c r="F10" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="20" t="s">
+      <c r="H10" s="19" t="s">
         <v>28</v>
       </c>
       <c r="J10" s="12"/>
     </row>
     <row r="11" spans="1:13" s="11" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="30" t="s">
+      <c r="C11" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="30" t="s">
+      <c r="D11" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" s="30" t="s">
+      <c r="E11" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="20" t="s">
+      <c r="H11" s="19" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1484,106 +1488,106 @@
       <c r="H12" s="17"/>
     </row>
     <row r="13" spans="1:13" s="11" customFormat="1" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="F13" s="30" t="s">
+      <c r="D13" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="G13" s="30" t="s">
+      <c r="G13" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="H13" s="20" t="s">
+      <c r="H13" s="19" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:13" s="11" customFormat="1" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="30" t="s">
+      <c r="D14" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="F14" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="G14" s="30" t="s">
+      <c r="E14" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G14" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="H14" s="20" t="s">
+      <c r="H14" s="19" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:13" s="11" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="51" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="G15" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="H15" s="30" t="s">
+      <c r="C15" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" s="29" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:13" s="11" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="G16" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="H16" s="30" t="s">
+      <c r="C16" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="H16" s="29" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1608,40 +1612,40 @@
       <c r="H18" s="17"/>
     </row>
     <row r="19" spans="1:8" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="38" t="s">
+      <c r="A19" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="34"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="35"/>
+      <c r="B19" s="33"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="34"/>
     </row>
     <row r="20" spans="1:8" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="52" t="s">
         <v>50</v>
       </c>
-      <c r="B20" s="32" t="s">
+      <c r="B20" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" s="52" t="s">
+      <c r="C20" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="E20" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="G20" s="52" t="s">
+      <c r="E20" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="H20" s="32" t="s">
+      <c r="H20" s="30" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1706,92 +1710,92 @@
       <c r="H26" s="17"/>
     </row>
     <row r="27" spans="1:8" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="38" t="s">
+      <c r="A27" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="34"/>
-      <c r="C27" s="34"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="35"/>
+      <c r="B27" s="33"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="34"/>
     </row>
     <row r="28" spans="1:8" s="11" customFormat="1" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="18" t="s">
+      <c r="A28" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="C28" s="30" t="s">
+      <c r="C28" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="D28" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="E28" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="F28" s="29" t="s">
+      <c r="D28" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="F28" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="G28" s="30" t="s">
+      <c r="G28" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="H28" s="20" t="s">
+      <c r="H28" s="19" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:8" s="11" customFormat="1" ht="99.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="18" t="s">
+      <c r="A29" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="C29" s="30" t="s">
+      <c r="C29" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="D29" s="30" t="s">
+      <c r="D29" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="E29" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="F29" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="G29" s="30" t="s">
+      <c r="E29" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G29" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="H29" s="20" t="s">
+      <c r="H29" s="19" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:8" s="11" customFormat="1" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="B30" s="19" t="s">
+      <c r="B30" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="C30" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="E30" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="F30" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="G30" s="30" t="s">
+      <c r="C30" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G30" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="H30" s="20" t="s">
+      <c r="H30" s="19" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1816,30 +1820,35 @@
       <c r="H32" s="17"/>
     </row>
     <row r="33" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="21"/>
+      <c r="A33" s="20"/>
     </row>
     <row r="34" spans="1:8" s="11" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="22"/>
-      <c r="B34" s="23"/>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="24"/>
-      <c r="H34" s="25"/>
+      <c r="A34" s="21"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="23"/>
+      <c r="H34" s="24"/>
     </row>
     <row r="35" spans="1:8" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="26"/>
-      <c r="B35" s="27"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28"/>
-      <c r="H35" s="28"/>
+      <c r="A35" s="25"/>
+      <c r="B35" s="26"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="27"/>
+      <c r="H35" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A5:H5"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="B6:B7"/>
@@ -1847,12 +1856,19 @@
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A5:H5"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A10" r:id="rId1" display="https://le-djok.github.io/portfolio/ap1.html" xr:uid="{08A01FA7-453E-4A38-8B65-49AE3CA16102}"/>
+    <hyperlink ref="A11" r:id="rId2" xr:uid="{651BC882-1D5A-4700-B544-BDF8A4F4EED7}"/>
+    <hyperlink ref="A13" r:id="rId3" display="https://le-djok.github.io/portfolio/ap2.html" xr:uid="{679B1937-B7B5-4E79-8D1B-18D7227F5BB1}"/>
+    <hyperlink ref="A14" r:id="rId4" xr:uid="{393AEF09-C53D-4D54-A88E-5D2060C5DEFD}"/>
+    <hyperlink ref="A15" r:id="rId5" display="https://le-djok.github.io/portfolio/veille.html" xr:uid="{468A5ACF-6722-44C3-89CE-223E7682BB2D}"/>
+    <hyperlink ref="A16" r:id="rId6" display="https://le-djok.github.io/portfolio/moi.html" xr:uid="{7FDA6D6E-79C1-4156-BE9A-AEE80E7A6C00}"/>
+    <hyperlink ref="A20" r:id="rId7" display="https://le-djok.github.io/portfolio/stage1.html" xr:uid="{DA14A851-2012-4265-B24A-0C37A51EB29E}"/>
+    <hyperlink ref="A28" r:id="rId8" display="https://le-djok.github.io/portfolio/situation1.html" xr:uid="{7A1713FA-FDF8-463C-8DF6-827DED6DED08}"/>
+    <hyperlink ref="A29" r:id="rId9" display="https://le-djok.github.io/portfolio/situation2.html" xr:uid="{D7587446-CBCE-4212-9CE4-21B37056C231}"/>
+    <hyperlink ref="A30" r:id="rId10" display="https://le-djok.github.io/portfolio/situation3.html" xr:uid="{06CA4D76-49FA-4A70-BF44-3E14A6694A49}"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.196527777777778" right="0.196527777777778" top="0.196527777777778" bottom="0.196527777777778" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
